--- a/event_registration_forms/030_event_program_printing_order_form--event_registration_forms.xlsx
+++ b/event_registration_forms/030_event_program_printing_order_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_3</t>
+          <t>event_program_printing_order_form_page_3_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_3</t>
+          <t>event_program_printing_order_form_page_3_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_2</t>
+          <t>event_program_printing_order_form_page_2_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_3</t>
+          <t>event_program_printing_order_form_page_3_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_2</t>
+          <t>event_program_printing_order_form_page_2_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_3</t>
+          <t>event_program_printing_order_form_page_3_5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total Cost</t>
+          <t>Event Program Printing Order Form Page 3 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -743,12 +743,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_3</t>
+          <t>event_program_printing_order_form_page_3_6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Total Cost</t>
+          <t>Event Program Printing Order Form Page 3 6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Total Cost</t>
+          <t>Event Program Printing Order Form Page 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_2</t>
+          <t>event_program_printing_order_form_page_2_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_2_choices</t>
+          <t>event_program_printing_order_form_page_2_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_program_printing_order_form_page_2_choices</t>
+          <t>event_program_printing_order_form_page_2_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
